--- a/utils/operator_name_list.xlsx
+++ b/utils/operator_name_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legen\Documents\python_project\endfield\skill_mul_survey2\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD6E92C-F89C-463E-8B11-84F70BF60C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A1354F-685A-4D01-B4A3-092C1570854A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9100" yWindow="1150" windowWidth="8680" windowHeight="9640" xr2:uid="{3F6101A8-1885-4154-974A-D078AE483AF0}"/>
+    <workbookView xWindow="1070" yWindow="980" windowWidth="8680" windowHeight="9640" xr2:uid="{3F6101A8-1885-4154-974A-D078AE483AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>lifeng</t>
     <phoneticPr fontId="1"/>
@@ -135,6 +135,10 @@
   </si>
   <si>
     <t>pogranichnik</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>zhuang_fangyi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -519,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3617CACC-A5AB-451D-8841-3A3FE55404B8}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -604,46 +608,51 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
